--- a/Employee_Reports_wi52/William Villanueva Gutierrez Q0426.xlsx
+++ b/Employee_Reports_wi52/William Villanueva Gutierrez Q0426.xlsx
@@ -454,7 +454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:K4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -569,11 +569,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -582,6 +582,43 @@
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>IS0 55001 (Other Trainings)</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr"/>
+      <c r="D4" s="3" t="inlineStr"/>
+      <c r="E4" s="3" t="inlineStr"/>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>26-Aug-2026</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>25-Aug-2028</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="n">
+        <v>728</v>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>27-Aug-2026</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
